--- a/Attendance/Present_06-11-2025.xlsx
+++ b/Attendance/Present_06-11-2025.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -517,6 +517,66 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>00:09:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>VENKATANATHAN P R</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>06-11-2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>08:34:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Parthiban P</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>06-11-2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Present</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>08:35:26</t>
         </is>
       </c>
     </row>
